--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\eclipse-workspace\OrangeHRMProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A27F7F-08BF-4A5F-BBD0-AC425F987A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA65320C-D760-4DB7-B1CE-223743FBD835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="validLoginData" sheetId="1" r:id="rId1"/>
@@ -47,10 +47,10 @@
     <t>emp_name</t>
   </si>
   <si>
-    <t>Hitendra</t>
-  </si>
-  <si>
-    <t>Admin</t>
+    <t>ravi_kanth</t>
+  </si>
+  <si>
+    <t>Ravi@@123</t>
   </si>
 </sst>
 </file>
@@ -396,10 +396,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\eclipse-workspace\OrangeHRMProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA65320C-D760-4DB7-B1CE-223743FBD835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE974BE7-567E-489D-B253-F62271629BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>username</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Ravi@@123</t>
+  </si>
+  <si>
+    <t>ravi</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/target/test-classes/testdata/TestData.xlsx
+++ b/target/test-classes/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\eclipse-workspace\OrangeHRMProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE974BE7-567E-489D-B253-F62271629BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1B9B2B-51D8-4641-804C-C84B6E26CD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="validLoginData" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>username</t>
   </si>
@@ -47,13 +47,10 @@
     <t>emp_name</t>
   </si>
   <si>
-    <t>ravi_kanth</t>
-  </si>
-  <si>
-    <t>Ravi@@123</t>
-  </si>
-  <si>
     <t>ravi</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
 </sst>
 </file>
@@ -399,10 +396,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -460,7 +457,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
